--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_71_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_71_IN_Piura.xlsx
@@ -1802,7 +1802,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>26.15</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" s="31">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>47.91</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>25.19</v>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="C13" s="21">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>0.75</v>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1919,11 +1919,11 @@
       </c>
       <c r="B15" s="44">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>10.6733</v>
       </c>
       <c r="C15" s="45">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D15" s="43" t="inlineStr">
         <is>
@@ -1944,11 +1944,11 @@
       </c>
       <c r="B16" s="47">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>7.9048</v>
       </c>
       <c r="C16" s="48">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>74.06</v>
       </c>
       <c r="D16" s="46" t="inlineStr">
         <is>
@@ -1969,11 +1969,11 @@
       </c>
       <c r="B17" s="47">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>2.7685</v>
       </c>
       <c r="C17" s="48">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>25.94</v>
       </c>
       <c r="D17" s="46" t="inlineStr">
         <is>
@@ -2129,11 +2129,11 @@
       </c>
       <c r="B27" s="22">
         <f>SUM(B25:B26)</f>
-        <v/>
+        <v>10.6756</v>
       </c>
       <c r="C27" s="23">
         <f>SUM(C25:C26)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D27" s="17" t="inlineStr"/>
       <c r="E27" s="17" t="inlineStr"/>
@@ -2252,6 +2252,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2398,6 +2399,7 @@
       <c r="F13" s="17" t="inlineStr"/>
       <c r="G13" s="17" t="inlineStr"/>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
@@ -2442,6 +2444,7 @@
       <c r="G16" s="8" t="n"/>
       <c r="H16" s="8" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18" ht="156" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
@@ -2859,11 +2862,11 @@
       </c>
       <c r="B18" s="33">
         <f>SUM(B10:B17)</f>
-        <v/>
+        <v>523.87</v>
       </c>
       <c r="C18" s="23">
         <f>SUM(C10:C17)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
@@ -2873,19 +2876,19 @@
       <c r="E18" s="17" t="inlineStr"/>
       <c r="F18" s="17">
         <f>ROUND(AVERAGE(F10:F17),2)</f>
-        <v/>
+        <v>28.06</v>
       </c>
       <c r="G18" s="22">
         <f>ROUND(AVERAGE(G10:G17),4)</f>
-        <v/>
+        <v>0.5477</v>
       </c>
       <c r="H18" s="23">
         <f>ROUND(AVERAGE(H10:H17),2)</f>
-        <v/>
+        <v>72.48</v>
       </c>
       <c r="I18" s="23">
         <f>ROUND(AVERAGE(I10:I17),2)</f>
-        <v/>
+        <v>31.88</v>
       </c>
     </row>
     <row r="19"/>
